--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N170_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N170_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.01852472789497</v>
+        <v>5.365510268282933</v>
       </c>
       <c r="D2" t="n">
-        <v>7.885134022006471</v>
+        <v>1.281334278576052</v>
       </c>
       <c r="E2" t="n">
-        <v>8.8102395094985</v>
+        <v>1.431663920293506</v>
       </c>
       <c r="F2" t="n">
-        <v>13.86611050268041</v>
+        <v>2.253242956685567</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.43580757439146</v>
+        <v>3.320818730838612</v>
       </c>
       <c r="D3" t="n">
-        <v>20.85093909263128</v>
+        <v>3.388277602552583</v>
       </c>
       <c r="E3" t="n">
-        <v>8.8102395094985</v>
+        <v>1.431663920293506</v>
       </c>
       <c r="F3" t="n">
-        <v>13.86611050268041</v>
+        <v>2.253242956685567</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63857533933002</v>
+        <v>6.928768492641129</v>
       </c>
       <c r="D4" t="n">
-        <v>43.63595996734833</v>
+        <v>7.090843494694103</v>
       </c>
       <c r="E4" t="n">
-        <v>8.8102395094985</v>
+        <v>1.431663920293506</v>
       </c>
       <c r="F4" t="n">
-        <v>13.86611050268041</v>
+        <v>2.253242956685567</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.40028472082931</v>
+        <v>7.865046267134764</v>
       </c>
       <c r="D5" t="n">
-        <v>48.20332448948534</v>
+        <v>7.833040229541368</v>
       </c>
       <c r="E5" t="n">
-        <v>8.8102395094985</v>
+        <v>1.431663920293506</v>
       </c>
       <c r="F5" t="n">
-        <v>13.86611050268041</v>
+        <v>2.253242956685567</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.69832460387206</v>
+        <v>6.12597774812921</v>
       </c>
       <c r="D6" t="n">
-        <v>39.0318069408796</v>
+        <v>6.342668627892935</v>
       </c>
       <c r="E6" t="n">
-        <v>8.8102395094985</v>
+        <v>1.431663920293506</v>
       </c>
       <c r="F6" t="n">
-        <v>13.86611050268041</v>
+        <v>2.253242956685567</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.22017966849962</v>
+        <v>5.235779196131189</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20555403050597</v>
+        <v>5.07090252995722</v>
       </c>
       <c r="E7" t="n">
-        <v>8.8102395094985</v>
+        <v>1.431663920293506</v>
       </c>
       <c r="F7" t="n">
-        <v>13.86611050268041</v>
+        <v>2.253242956685567</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
